--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487816_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487816_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2018</v>
+        <v>4.6623</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0995</v>
+        <v>4.7361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1024</v>
+        <v>-0.0738</v>
       </c>
       <c r="G2" t="n">
         <v>0.7023</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1437</v>
+        <v>0.6041</v>
       </c>
       <c r="T2" t="n">
-        <v>0.944</v>
+        <v>0.5806</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1997</v>
+        <v>0.0235</v>
       </c>
       <c r="V2" t="n">
         <v>3.9802</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8518</v>
+        <v>3.2701</v>
       </c>
       <c r="E3" t="n">
-        <v>5.138</v>
+        <v>5.6738</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2862</v>
+        <v>-2.4037</v>
       </c>
       <c r="G3" t="n">
         <v>1.1349</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3237</v>
+        <v>-0.9054</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4972</v>
+        <v>0.0386</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8265</v>
+        <v>-0.944</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6829</v>
+        <v>1.9468</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5693</v>
+        <v>0.9166</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8864</v>
+        <v>1.0303</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0247</v>
+        <v>1.2978</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7526</v>
+        <v>0.9892</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7773</v>
+        <v>0.3086</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2244</v>
+        <v>1.8123</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8996</v>
+        <v>1.1853</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6752</v>
+        <v>0.627</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2492</v>
+        <v>-0.5144</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.147</v>
+        <v>-0.196</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1022</v>
+        <v>-0.3184</v>
       </c>
       <c r="P4" t="n">
         <v>0.8325</v>
@@ -766,28 +766,28 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1052</v>
+        <v>0.2765</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1149</v>
+        <v>-0.1881</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0097</v>
+        <v>0.4645</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4599</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5536</v>
+        <v>0.8807</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4646</v>
+        <v>1.8845</v>
       </c>
       <c r="F5" t="n">
-        <v>1.089</v>
+        <v>-1.0038</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2978</v>
+        <v>-0.0247</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9892</v>
+        <v>1.7526</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3086</v>
+        <v>-1.7773</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8123</v>
+        <v>1.2244</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1853</v>
+        <v>1.8996</v>
       </c>
       <c r="L5" t="n">
-        <v>0.627</v>
+        <v>-0.6752</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5144</v>
+        <v>-1.2492</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.196</v>
+        <v>-0.147</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3184</v>
+        <v>-1.1022</v>
       </c>
       <c r="P5" t="n">
         <v>0.8325</v>
@@ -844,22 +844,22 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1168</v>
+        <v>0.3029</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.64</v>
+        <v>0.4301</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5233</v>
+        <v>-0.1272</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X5" t="n">
         <v>-0.4599</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.7076</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.2477</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2946</v>
+        <v>0.5001</v>
       </c>
       <c r="E6" t="n">
         <v>3.9474</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.6528</v>
+        <v>-3.4473</v>
       </c>
       <c r="G6" t="n">
         <v>0.0801</v>
@@ -922,13 +922,13 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2017</v>
+        <v>-0.9962</v>
       </c>
       <c r="T6" t="n">
         <v>0.2824</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4842</v>
+        <v>-1.2786</v>
       </c>
       <c r="V6" t="n">
         <v>0.5838</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3011</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0286</v>
+        <v>1.5225</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3296</v>
+        <v>-1.4471</v>
       </c>
       <c r="G7" t="n">
         <v>0.8361</v>
@@ -1000,13 +1000,13 @@
         <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1808</v>
+        <v>-0.8044</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5624</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.7358</v>
       </c>
       <c r="V7" t="n">
         <v>0.4599</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4675</v>
+        <v>-0.2658</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8381</v>
+        <v>-0.6657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3706</v>
+        <v>0.3999</v>
       </c>
       <c r="G8" t="n">
         <v>0.2857</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0457</v>
+        <v>0.1561</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1305</v>
+        <v>0.0419</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0848</v>
+        <v>0.1142</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7076</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9944</v>
+        <v>-0.5131</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4416</v>
+        <v>-1.9897</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4472</v>
+        <v>1.4765</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1973</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4214</v>
+        <v>0.0599</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0576</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0881</v>
+        <v>0.1175</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7156</v>
+        <v>-1.5497</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9054</v>
+        <v>-0.7983</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8102</v>
+        <v>-0.7514</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4161</v>
@@ -1234,13 +1234,13 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2995</v>
+        <v>-0.1336</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0385</v>
+        <v>0.0202</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9836</v>
+        <v>-3.2948</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9789</v>
+        <v>-1.4076</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0047</v>
+        <v>-1.8872</v>
       </c>
       <c r="G11" t="n">
         <v>0.5568</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6237</v>
+        <v>-0.9349</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1924</v>
+        <v>-0.2362</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8161</v>
+        <v>-0.6987</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0437</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3366</v>
+        <v>-5.446</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2036</v>
+        <v>-2.4598</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.133</v>
+        <v>-2.9862</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5398</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4332</v>
+        <v>0.3237</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2701</v>
+        <v>0.0138</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1631</v>
+        <v>0.3099</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9813</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.110200000000001</v>
+        <v>-7.9378</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.3283</v>
+        <v>-6.1559</v>
       </c>
       <c r="F13" t="n">
         <v>-1.7818</v>
@@ -1468,10 +1468,10 @@
         <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3262</v>
+        <v>-0.1538</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1743</v>
+        <v>-0.0019</v>
       </c>
       <c r="U13" t="n">
         <v>-0.152</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.324300000000001</v>
+        <v>-7.6718</v>
       </c>
       <c r="E14" t="n">
-        <v>4.551500000000002</v>
+        <v>5.203900000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.8755</v>
+        <v>-12.8756</v>
       </c>
       <c r="G14" t="n">
         <v>-8.6332</v>
@@ -1546,13 +1546,13 @@
         <v>14.5684</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.857400000000001</v>
+        <v>-2.2051</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0287999999999998</v>
+        <v>0.6813</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.8864</v>
+        <v>-2.8865</v>
       </c>
       <c r="V14" t="n">
         <v>3.1664</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.209</v>
+        <v>9.054399999999999</v>
       </c>
       <c r="E15" t="n">
         <v>6.8969</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3121</v>
+        <v>2.1574</v>
       </c>
       <c r="G15" t="n">
         <v>6.8408</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2194</v>
+        <v>1.0647</v>
       </c>
       <c r="T15" t="n">
         <v>0.2048</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0146</v>
+        <v>0.8599</v>
       </c>
       <c r="V15" t="n">
         <v>1.9813</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.7303</v>
+        <v>6.7763</v>
       </c>
       <c r="E16" t="n">
-        <v>6.6514</v>
+        <v>6.4371</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0789</v>
+        <v>0.3392</v>
       </c>
       <c r="G16" t="n">
         <v>6.0325</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1683</v>
+        <v>0.2143</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4782</v>
+        <v>0.2639</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3099</v>
+        <v>-0.0496</v>
       </c>
       <c r="V16" t="n">
         <v>0.1132</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.8963</v>
+        <v>5.3567</v>
       </c>
       <c r="E17" t="n">
-        <v>4.5597</v>
+        <v>4.8812</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3365</v>
+        <v>0.4755</v>
       </c>
       <c r="G17" t="n">
         <v>3.3067</v>
@@ -1780,13 +1780,13 @@
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4241</v>
+        <v>0.8845</v>
       </c>
       <c r="T17" t="n">
-        <v>0.152</v>
+        <v>0.4734</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2721</v>
+        <v>0.4111</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7076</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5574</v>
+        <v>1.5359</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3199</v>
+        <v>1.8913</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7625</v>
+        <v>-0.3554</v>
       </c>
       <c r="G18" t="n">
         <v>0.9931</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5643</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7887</v>
+        <v>0.3601</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2244</v>
+        <v>0.1827</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.289</v>
+        <v>1.3685</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7607</v>
+        <v>2.6471</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5284</v>
+        <v>-1.2786</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2236</v>
+        <v>2.4747</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9597</v>
+        <v>1.6567</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1832</v>
+        <v>0.8181</v>
       </c>
       <c r="J19" t="n">
-        <v>1.032</v>
+        <v>3.5077</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8981</v>
+        <v>2.7631</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9301</v>
+        <v>0.7446</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8085</v>
+        <v>-1.0329</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0616</v>
+        <v>-1.1064</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2531</v>
+        <v>0.0735</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8731</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6035</v>
+        <v>0.2694</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5153</v>
+        <v>0.18</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0881</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>2.3351</v>
+        <v>-1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7677</v>
+        <v>1.0684</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2185</v>
+        <v>0.2249</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4508</v>
+        <v>0.8435</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4747</v>
+        <v>0.2236</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6567</v>
+        <v>-2.9597</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8181</v>
+        <v>3.1832</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5077</v>
+        <v>1.032</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7631</v>
+        <v>-1.8981</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7446</v>
+        <v>2.9301</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0329</v>
+        <v>-0.8085</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1064</v>
+        <v>-1.0616</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0735</v>
+        <v>0.2531</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3314</v>
+        <v>0.3828</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2486</v>
+        <v>-0.0204</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0828</v>
+        <v>0.4032</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6378</v>
+        <v>-1.2811</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9898</v>
+        <v>-1.0134</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6276</v>
+        <v>-0.2677</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9781</v>
+        <v>-2.0772</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6948</v>
+        <v>-2.6993</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2833</v>
+        <v>0.6221</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0102</v>
+        <v>-0.6196</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1343</v>
+        <v>-0.7763</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1445</v>
+        <v>0.1568</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9679</v>
+        <v>-1.4576</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8291</v>
+        <v>-1.923</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1388</v>
+        <v>0.4654</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3759</v>
+        <v>-0.0039</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5807</v>
+        <v>-0.1462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2048</v>
+        <v>0.1423</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.868</v>
+        <v>-0.2406</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4599</v>
+        <v>-0.2477</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.328</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7645</v>
+        <v>-1.9145</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4421</v>
+        <v>-2.0075</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3225</v>
+        <v>0.093</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0772</v>
+        <v>-1.7759</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6993</v>
+        <v>-0.5733</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6221</v>
+        <v>-1.2026</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6196</v>
+        <v>-1.3022</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7763</v>
+        <v>0.1535</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1568</v>
+        <v>-1.4557</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4576</v>
+        <v>-0.4737</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.923</v>
+        <v>-0.7268</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4654</v>
+        <v>0.2531</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4873</v>
+        <v>-0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5748</v>
+        <v>0.3353</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.3353</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2406</v>
+        <v>-0.3467</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0071</v>
+        <v>-0.3467</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0123</v>
+        <v>-1.9472</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7696</v>
+        <v>-0.8767</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2427</v>
+        <v>-1.0705</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3175</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>0.122</v>
+        <v>0.1871</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06</v>
+        <v>0.2323</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8574</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7209</v>
+        <v>-2.2093</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4361</v>
+        <v>0.1326</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2848</v>
+        <v>-2.3419</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7759</v>
+        <v>-1.9781</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5733</v>
+        <v>-1.6948</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2026</v>
+        <v>-0.2833</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3022</v>
+        <v>-0.0102</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1535</v>
+        <v>0.1343</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4557</v>
+        <v>-0.1445</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4737</v>
+        <v>-1.9679</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7268</v>
+        <v>-1.8291</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2531</v>
+        <v>-0.1388</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8064</v>
+        <v>0.8044</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.7235</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7131</v>
+        <v>0.0809</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3467</v>
+        <v>-1.868</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3467</v>
+        <v>-2.328</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.99</v>
+        <v>-7.3407</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8736</v>
+        <v>-6.3378</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1164</v>
+        <v>-1.0029</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0897</v>
@@ -2404,13 +2404,13 @@
         <v>1.6649</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0052</v>
+        <v>0.6545</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0215</v>
+        <v>0.5573</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0163</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4081</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.324199999999999</v>
+        <v>10.4674</v>
       </c>
       <c r="E26" t="n">
-        <v>12.8755</v>
+        <v>12.8757</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.5514</v>
+        <v>-2.4084</v>
       </c>
       <c r="G26" t="n">
         <v>8.633000000000003</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.1232</v>
+        <v>-3.123200000000002</v>
       </c>
       <c r="I26" t="n">
         <v>11.7563</v>
@@ -2482,13 +2482,13 @@
         <v>14.5683</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8576</v>
+        <v>5.000599999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8864</v>
+        <v>2.8865</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.02900000000000004</v>
+        <v>2.1141</v>
       </c>
       <c r="V26" t="n">
         <v>-3.1663</v>
